--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -459,7 +459,7 @@
     <t>Pass:17 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-07-27</t>
+    <t>Last Updated: 2026-07-30</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="147">
   <si>
     <t>TC ID</t>
   </si>
@@ -79,7 +79,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Pass</t>
+    <t/>
   </si>
   <si>
     <t>On the Search screen with the grid loaded (office 1604)</t>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>Clicking each of the 4 Export variants opens the shared "Export" dialog.</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>2. Confirm a dialog titled "Export" renders with a Year(s) dropdown, a Currency dropdown, and Cancel / Continue / Close buttons, with Continue disabled at open</t>
@@ -456,10 +453,10 @@
     <t>Automated: 17 / Pending: 0</t>
   </si>
   <si>
-    <t>Pass:17 Fail:0 Skipped:0 Blocked:0</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-07-30</t>
+    <t>Not run in this delivery</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-08-07</t>
   </si>
 </sst>
 </file>
@@ -858,7 +855,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="10" width="57" customWidth="1"/>
     <col min="11" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
@@ -943,56 +940,56 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1001,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -1016,65 +1013,65 @@
         <v>21</v>
       </c>
       <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>32</v>
       </c>
-      <c r="L4" t="s">
-        <v>33</v>
-      </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" t="s">
         <v>34</v>
       </c>
-      <c r="L5" t="s">
-        <v>35</v>
-      </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
         <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -1083,7 +1080,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -1098,65 +1095,65 @@
         <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
         <v>38</v>
       </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -1165,7 +1162,7 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -1180,65 +1177,65 @@
         <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" t="s">
         <v>43</v>
       </c>
-      <c r="L8" t="s">
-        <v>44</v>
-      </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
         <v>46</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1247,7 +1244,7 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -1262,106 +1259,106 @@
         <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" t="s">
         <v>48</v>
       </c>
-      <c r="L10" t="s">
-        <v>49</v>
-      </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" t="s">
         <v>50</v>
       </c>
-      <c r="L11" t="s">
-        <v>51</v>
-      </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
         <v>52</v>
       </c>
-      <c r="L12" t="s">
-        <v>53</v>
-      </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
         <v>54</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1370,7 +1367,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -1385,65 +1382,65 @@
         <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" t="s">
         <v>56</v>
       </c>
-      <c r="L13" t="s">
-        <v>57</v>
-      </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -1452,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -1467,229 +1464,229 @@
         <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" t="s">
         <v>61</v>
       </c>
-      <c r="L15" t="s">
-        <v>62</v>
-      </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" t="s">
         <v>63</v>
       </c>
-      <c r="L16" t="s">
-        <v>64</v>
-      </c>
       <c r="M16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s">
+        <v>64</v>
+      </c>
+      <c r="L17" t="s">
         <v>65</v>
       </c>
-      <c r="L17" t="s">
-        <v>66</v>
-      </c>
       <c r="M17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s">
+        <v>66</v>
+      </c>
+      <c r="L18" t="s">
         <v>67</v>
       </c>
-      <c r="L18" t="s">
-        <v>68</v>
-      </c>
       <c r="M18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19" t="s">
         <v>69</v>
       </c>
-      <c r="L19" t="s">
-        <v>70</v>
-      </c>
       <c r="M19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" t="s">
         <v>71</v>
       </c>
-      <c r="L20" t="s">
-        <v>72</v>
-      </c>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
       </c>
       <c r="C21" t="s">
         <v>15</v>
@@ -1698,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -1713,65 +1710,65 @@
         <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" t="s">
         <v>75</v>
       </c>
-      <c r="L21" t="s">
-        <v>76</v>
-      </c>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" t="s">
         <v>77</v>
       </c>
-      <c r="L22" t="s">
-        <v>78</v>
-      </c>
       <c r="M22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -1780,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -1798,62 +1795,62 @@
         <v>22</v>
       </c>
       <c r="K23" t="s">
+        <v>80</v>
+      </c>
+      <c r="L23" t="s">
         <v>81</v>
       </c>
-      <c r="L23" t="s">
-        <v>82</v>
-      </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s">
+        <v>82</v>
+      </c>
+      <c r="L24" t="s">
         <v>83</v>
       </c>
-      <c r="L24" t="s">
-        <v>84</v>
-      </c>
       <c r="M24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" t="s">
         <v>85</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -1862,7 +1859,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -1880,144 +1877,144 @@
         <v>22</v>
       </c>
       <c r="K25" t="s">
+        <v>86</v>
+      </c>
+      <c r="L25" t="s">
         <v>87</v>
       </c>
-      <c r="L25" t="s">
-        <v>88</v>
-      </c>
       <c r="M25" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s">
+        <v>88</v>
+      </c>
+      <c r="L26" t="s">
         <v>89</v>
       </c>
-      <c r="L26" t="s">
-        <v>90</v>
-      </c>
       <c r="M26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s">
+        <v>90</v>
+      </c>
+      <c r="L27" t="s">
         <v>91</v>
       </c>
-      <c r="L27" t="s">
-        <v>92</v>
-      </c>
       <c r="M27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s">
+        <v>92</v>
+      </c>
+      <c r="L28" t="s">
         <v>93</v>
       </c>
-      <c r="L28" t="s">
-        <v>94</v>
-      </c>
       <c r="M28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
         <v>95</v>
-      </c>
-      <c r="B29" t="s">
-        <v>96</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
@@ -2026,7 +2023,7 @@
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -2044,144 +2041,144 @@
         <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L31" t="s">
         <v>99</v>
       </c>
-      <c r="L31" t="s">
-        <v>100</v>
-      </c>
       <c r="M31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s">
+        <v>92</v>
+      </c>
+      <c r="L32" t="s">
         <v>93</v>
       </c>
-      <c r="L32" t="s">
-        <v>94</v>
-      </c>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -2190,7 +2187,7 @@
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -2208,144 +2205,144 @@
         <v>22</v>
       </c>
       <c r="K33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L33" t="s">
         <v>103</v>
       </c>
-      <c r="L33" t="s">
-        <v>104</v>
-      </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s">
+        <v>104</v>
+      </c>
+      <c r="L34" t="s">
         <v>105</v>
       </c>
-      <c r="L34" t="s">
-        <v>106</v>
-      </c>
       <c r="M34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s">
+        <v>107</v>
+      </c>
+      <c r="L36" t="s">
         <v>108</v>
       </c>
-      <c r="L36" t="s">
-        <v>109</v>
-      </c>
       <c r="M36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" t="s">
         <v>110</v>
-      </c>
-      <c r="B37" t="s">
-        <v>111</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -2354,7 +2351,7 @@
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -2372,144 +2369,144 @@
         <v>22</v>
       </c>
       <c r="K37" t="s">
+        <v>111</v>
+      </c>
+      <c r="L37" t="s">
         <v>112</v>
       </c>
-      <c r="L37" t="s">
-        <v>113</v>
-      </c>
       <c r="M37" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s">
+        <v>114</v>
+      </c>
+      <c r="L40" t="s">
         <v>115</v>
       </c>
-      <c r="L40" t="s">
-        <v>116</v>
-      </c>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" t="s">
         <v>117</v>
-      </c>
-      <c r="B41" t="s">
-        <v>118</v>
       </c>
       <c r="C41" t="s">
         <v>15</v>
@@ -2518,7 +2515,7 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
@@ -2536,62 +2533,62 @@
         <v>22</v>
       </c>
       <c r="K41" t="s">
+        <v>118</v>
+      </c>
+      <c r="L41" t="s">
         <v>119</v>
       </c>
-      <c r="L41" t="s">
-        <v>120</v>
-      </c>
       <c r="M41" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s">
+        <v>120</v>
+      </c>
+      <c r="L42" t="s">
         <v>121</v>
       </c>
-      <c r="L42" t="s">
-        <v>122</v>
-      </c>
       <c r="M42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43" t="s">
         <v>123</v>
-      </c>
-      <c r="B43" t="s">
-        <v>124</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -2600,7 +2597,7 @@
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -2618,103 +2615,103 @@
         <v>22</v>
       </c>
       <c r="K43" t="s">
+        <v>124</v>
+      </c>
+      <c r="L43" t="s">
         <v>125</v>
       </c>
-      <c r="L43" t="s">
-        <v>126</v>
-      </c>
       <c r="M43" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s">
+        <v>126</v>
+      </c>
+      <c r="L44" t="s">
         <v>127</v>
       </c>
-      <c r="L44" t="s">
-        <v>128</v>
-      </c>
       <c r="M44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s">
+        <v>128</v>
+      </c>
+      <c r="L45" t="s">
         <v>129</v>
       </c>
-      <c r="L45" t="s">
-        <v>130</v>
-      </c>
       <c r="M45" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" t="s">
         <v>131</v>
-      </c>
-      <c r="B46" t="s">
-        <v>132</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -2723,7 +2720,7 @@
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -2741,62 +2738,62 @@
         <v>22</v>
       </c>
       <c r="K46" t="s">
+        <v>132</v>
+      </c>
+      <c r="L46" t="s">
         <v>133</v>
       </c>
-      <c r="L46" t="s">
-        <v>134</v>
-      </c>
       <c r="M46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s">
+        <v>134</v>
+      </c>
+      <c r="L47" t="s">
         <v>135</v>
       </c>
-      <c r="L47" t="s">
-        <v>136</v>
-      </c>
       <c r="M47" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" t="s">
         <v>137</v>
-      </c>
-      <c r="B48" t="s">
-        <v>138</v>
       </c>
       <c r="C48" t="s">
         <v>15</v>
@@ -2805,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F48" t="s">
         <v>18</v>
@@ -2823,95 +2820,95 @@
         <v>22</v>
       </c>
       <c r="K48" t="s">
+        <v>138</v>
+      </c>
+      <c r="L48" t="s">
         <v>139</v>
       </c>
-      <c r="L48" t="s">
-        <v>140</v>
-      </c>
       <c r="M48" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s">
+        <v>140</v>
+      </c>
+      <c r="L49" t="s">
         <v>141</v>
       </c>
-      <c r="L49" t="s">
-        <v>142</v>
-      </c>
       <c r="M49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="I51" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="J51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_pricing_export_all" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="149">
   <si>
     <t>TC ID</t>
   </si>
@@ -79,16 +80,19 @@
     <t>Automated</t>
   </si>
   <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>On the Search screen with the grid loaded (office 1604)</t>
+  </si>
+  <si>
+    <t>1. For each of the 4 Export variants: open Export and click the variant</t>
+  </si>
+  <si>
+    <t>Clicking each of the 4 Export variants opens the shared "Export" dialog.</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>On the Search screen with the grid loaded (office 1604)</t>
-  </si>
-  <si>
-    <t>1. For each of the 4 Export variants: open Export and click the variant</t>
-  </si>
-  <si>
-    <t>Clicking each of the 4 Export variants opens the shared "Export" dialog.</t>
   </si>
   <si>
     <t>2. Confirm a dialog titled "Export" renders with a Year(s) dropdown, a Currency dropdown, and Cancel / Continue / Close buttons, with Continue disabled at open</t>
@@ -453,10 +457,13 @@
     <t>Automated: 17 / Pending: 0</t>
   </si>
   <si>
-    <t>Not run in this delivery</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-08-07</t>
+    <t>Pass:17 Fail:0 Skipped:0 Blocked:0</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-08-12</t>
+  </si>
+  <si>
+    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
   </si>
 </sst>
 </file>
@@ -855,7 +862,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
     <col min="10" max="10" width="57" customWidth="1"/>
     <col min="11" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
@@ -940,56 +947,56 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -998,7 +1005,7 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -1013,65 +1020,65 @@
         <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -1080,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -1095,65 +1102,65 @@
         <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -1162,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -1177,65 +1184,65 @@
         <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1244,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -1259,106 +1266,106 @@
         <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1367,7 +1374,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -1382,65 +1389,65 @@
         <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -1449,7 +1456,7 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -1464,229 +1471,229 @@
         <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
         <v>15</v>
@@ -1695,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -1710,65 +1717,65 @@
         <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -1777,7 +1784,7 @@
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -1795,62 +1802,62 @@
         <v>22</v>
       </c>
       <c r="K23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -1859,7 +1866,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -1877,144 +1884,144 @@
         <v>22</v>
       </c>
       <c r="K25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
@@ -2023,7 +2030,7 @@
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -2041,144 +2048,144 @@
         <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -2187,7 +2194,7 @@
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -2205,144 +2212,144 @@
         <v>22</v>
       </c>
       <c r="K33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -2351,7 +2358,7 @@
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -2369,144 +2376,144 @@
         <v>22</v>
       </c>
       <c r="K37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M37" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M38" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
         <v>15</v>
@@ -2515,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
@@ -2533,62 +2540,62 @@
         <v>22</v>
       </c>
       <c r="K41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L41" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M41" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L42" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -2597,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -2615,103 +2622,103 @@
         <v>22</v>
       </c>
       <c r="K43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M43" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -2720,7 +2727,7 @@
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -2738,62 +2745,62 @@
         <v>22</v>
       </c>
       <c r="K46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
         <v>15</v>
@@ -2802,7 +2809,7 @@
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
         <v>18</v>
@@ -2820,95 +2827,111 @@
         <v>22</v>
       </c>
       <c r="K48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M48" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K49" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
+    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
+    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
+    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>f9d696e3767564ce556785ab32c8d4d620422045a781f574890b1a82aec41d64</t>
+    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
+    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -463,7 +463,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-export-all.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_pricing_export_all" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="148">
   <si>
     <t>TC ID</t>
   </si>
@@ -461,9 +460,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-08-12</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -2922,20 +2918,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>